--- a/data/trans_bre/P38A-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P38A-Clase-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 5,03</t>
+          <t>-3,38; 5,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 10,45</t>
+          <t>1,82; 10,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 6,4</t>
+          <t>-1,37; 7,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 5,7</t>
+          <t>-3,68; 6,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 12,36</t>
+          <t>2,02; 12,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 7,5</t>
+          <t>-1,5; 8,73</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 7,68</t>
+          <t>-0,37; 7,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 6,77</t>
+          <t>-2,18; 6,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 4,73</t>
+          <t>-4,61; 4,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 8,65</t>
+          <t>-0,33; 8,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 7,93</t>
+          <t>-2,42; 7,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 5,41</t>
+          <t>-5,08; 4,93</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 5,42</t>
+          <t>-3,19; 5,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 8,83</t>
+          <t>-0,82; 9,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 73,04</t>
+          <t>2,3; 69,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 6,1</t>
+          <t>-3,51; 6,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 10,33</t>
+          <t>-0,91; 10,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 363,98</t>
+          <t>2,56; 300,71</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 3,71</t>
+          <t>-2,26; 3,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 5,19</t>
+          <t>-0,61; 4,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 12,49</t>
+          <t>3,69; 11,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 4,3</t>
+          <t>-2,53; 4,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 6,07</t>
+          <t>-0,75; 5,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 15,19</t>
+          <t>4,19; 14,17</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,04; 13,71</t>
+          <t>5,88; 14,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,86; 11,23</t>
+          <t>3,75; 11,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 8,22</t>
+          <t>-21,51; 8,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,96; 17,09</t>
+          <t>6,87; 17,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 14,11</t>
+          <t>4,49; 14,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-26,96; 9,92</t>
+          <t>-25,65; 10,44</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,87; 41,6</t>
+          <t>29,55; 41,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,31; 40,99</t>
+          <t>28,26; 41,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,43; 50,86</t>
+          <t>28,86; 51,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50,6; 91,34</t>
+          <t>52,26; 94,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47,27; 85,78</t>
+          <t>47,55; 86,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54,06; 150,04</t>
+          <t>52,62; 151,58</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,14</t>
+          <t>2,8; 5,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,9</t>
+          <t>4,65; 7,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,66; 31,3</t>
+          <t>3,39; 28,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,24; 7,3</t>
+          <t>3,21; 6,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,38; 9,53</t>
+          <t>5,5; 9,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,4; 55,1</t>
+          <t>4,04; 46,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P38A-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P38A-Clase-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,32</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 5,56</t>
+          <t>-3,21; 5,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 10,29</t>
+          <t>2,04; 10,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 7,38</t>
+          <t>-1,47; 6,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 6,26</t>
+          <t>-3,46; 5,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 12,19</t>
+          <t>2,28; 12,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 8,73</t>
+          <t>-1,6; 7,71</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 7,43</t>
+          <t>-0,31; 7,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 6,79</t>
+          <t>-2,56; 7,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 4,31</t>
+          <t>-3,34; 5,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 8,49</t>
+          <t>-0,3; 8,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 7,93</t>
+          <t>-2,82; 8,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 4,93</t>
+          <t>-3,65; 6,01</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36,55</t>
+          <t>4,4</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 5,26</t>
+          <t>-2,91; 5,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 9,01</t>
+          <t>-0,71; 9,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 69,48</t>
+          <t>-0,52; 8,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 6,03</t>
+          <t>-3,15; 6,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 10,41</t>
+          <t>-0,82; 10,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,56; 300,71</t>
+          <t>-0,52; 9,91</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,42</t>
+          <t>5,57</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 3,71</t>
+          <t>-2,26; 4,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 4,97</t>
+          <t>-0,85; 5,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,69; 11,91</t>
+          <t>2,4; 8,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,22</t>
+          <t>-2,58; 4,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 5,8</t>
+          <t>-0,97; 5,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,19; 14,17</t>
+          <t>2,7; 10,43</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,37</t>
+          <t>10,86</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,44%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -954,39 +954,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 14,14</t>
+          <t>5,93; 13,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 11,57</t>
+          <t>3,96; 11,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 8,61</t>
+          <t>6,54; 14,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,87; 17,78</t>
+          <t>6,94; 17,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 14,72</t>
+          <t>4,65; 13,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,65; 10,44</t>
+          <t>8,01; 19,37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>40,18</t>
+          <t>40,31</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>95,97%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29,55; 41,96</t>
+          <t>29,27; 42,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,26; 41,11</t>
+          <t>27,86; 40,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28,86; 51,22</t>
+          <t>29,74; 49,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52,26; 94,24</t>
+          <t>52,06; 94,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>47,55; 86,03</t>
+          <t>47,25; 85,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52,62; 151,58</t>
+          <t>57,94; 151,76</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,7</t>
+          <t>5,85</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,86</t>
+          <t>2,89; 6,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,93</t>
+          <t>4,41; 7,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 28,06</t>
+          <t>3,98; 7,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,93</t>
+          <t>3,34; 7,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 9,63</t>
+          <t>5,16; 9,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,04; 46,23</t>
+          <t>4,77; 9,67</t>
         </is>
       </c>
     </row>
